--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_72_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_72_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>9.64</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="31">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>49.01</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>40.7</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>12.3984</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>7.2711</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>58.65</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>5.1273</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>41.35</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2123,11 +2123,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>12.4002</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2246,6 +2246,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2528,6 +2529,7 @@
       <c r="F17" s="17" t="inlineStr"/>
       <c r="G17" s="17" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -2572,6 +2574,7 @@
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22" ht="168" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
@@ -3096,11 +3099,11 @@
       </c>
       <c r="B21" s="33">
         <f>SUM(B10:B20)</f>
-        <v/>
+        <v>481.17</v>
       </c>
       <c r="C21" s="23">
         <f>SUM(C10:C20)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
@@ -3110,19 +3113,19 @@
       <c r="E21" s="17" t="inlineStr"/>
       <c r="F21" s="17">
         <f>ROUND(AVERAGE(F10:F20),2)</f>
-        <v/>
+        <v>29.39</v>
       </c>
       <c r="G21" s="22">
         <f>ROUND(AVERAGE(G10:G20),4)</f>
-        <v/>
+        <v>0.5435</v>
       </c>
       <c r="H21" s="23">
         <f>ROUND(AVERAGE(H10:H20),2)</f>
-        <v/>
+        <v>73.58</v>
       </c>
       <c r="I21" s="23">
         <f>ROUND(AVERAGE(I10:I20),2)</f>
-        <v/>
+        <v>32.8</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
